--- a/data/2026/15-covasna/63394-sfantu-gheorghe/budget_file.xlsx
+++ b/data/2026/15-covasna/63394-sfantu-gheorghe/budget_file.xlsx
@@ -26787,39 +26787,33 @@
       </c>
     </row>
     <row r="818">
-      <c r="A818" s="3" t="inlineStr">
+      <c r="A818" t="inlineStr">
         <is>
           <t>84.02</t>
         </is>
       </c>
-      <c r="B818" s="3" t="n"/>
-      <c r="C818" s="3" t="inlineStr">
+      <c r="C818" t="inlineStr">
         <is>
           <t>Transporturi (cod 84.02.03+84.02.04+84.02.06+84.02.50)</t>
         </is>
       </c>
-      <c r="D818" s="3" t="n">
+      <c r="D818" t="n">
         <v>10242</v>
       </c>
-      <c r="E818" s="3" t="n">
+      <c r="E818" t="n">
         <v>19</v>
       </c>
-      <c r="F818" s="3" t="inlineStr">
+      <c r="F818" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G818" s="4" t="n">
+      <c r="G818" s="2" t="n">
         <v>72143520</v>
       </c>
-      <c r="H818" s="3" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I818" s="3" t="inlineStr">
-        <is>
-          <t>84.02 total_2026: parent 72.143.520,00 != sum(children) 10.670.000,00 (2 children)</t>
+      <c r="H818" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
@@ -27648,26 +27642,31 @@
       </c>
     </row>
     <row r="842">
-      <c r="A842" t="inlineStr">
+      <c r="A842" s="3" t="inlineStr">
         <is>
           <t>60.03.70</t>
         </is>
       </c>
-      <c r="C842" s="7" t="inlineStr">
+      <c r="B842" s="3" t="n"/>
+      <c r="C842" s="8" t="inlineStr">
         <is>
           <t>Sume aferente TVA CHELTUIELI DE CAPITAL</t>
         </is>
       </c>
-      <c r="E842" t="n">
+      <c r="D842" s="3" t="n"/>
+      <c r="E842" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="F842" t="inlineStr"/>
-      <c r="G842" s="2" t="n">
-        <v>5073090007439730</v>
-      </c>
-      <c r="H842" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="F842" s="3" t="inlineStr"/>
+      <c r="G842" s="4" t="n"/>
+      <c r="H842" s="3" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I842" s="3" t="inlineStr">
+        <is>
+          <t>unparseable cell '5.073.090,00 7.439.730,00' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -28946,105 +28945,105 @@
       </c>
     </row>
     <row r="883">
-      <c r="A883" t="inlineStr">
+      <c r="A883" s="3" t="inlineStr">
         <is>
           <t>07.02</t>
         </is>
       </c>
-      <c r="C883" t="inlineStr">
+      <c r="B883" s="3" t="n"/>
+      <c r="C883" s="3" t="inlineStr">
         <is>
           <t>Impozite si taxe pe proprietate (cod 07.02.01+07.02.02+07.02.03+07.02.50)</t>
         </is>
       </c>
-      <c r="D883" t="n">
+      <c r="D883" s="3" t="n">
         <v>20024</v>
       </c>
-      <c r="E883" t="n">
+      <c r="E883" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="F883" t="inlineStr">
+      <c r="F883" s="3" t="inlineStr">
         <is>
           <t>revenue</t>
         </is>
       </c>
-      <c r="G883" s="2" t="n">
+      <c r="G883" s="4" t="n">
         <v>32200000</v>
       </c>
-      <c r="H883" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="H883" s="3" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I883" s="3" t="inlineStr">
+        <is>
+          <t>07.02 total_2026: parent 32.200.000,00 != sum(children) 26.500.000,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="884">
-      <c r="A884" s="5" t="inlineStr">
-        <is>
-          <t>07.02.50</t>
-        </is>
-      </c>
-      <c r="B884" s="5" t="n"/>
-      <c r="C884" s="5" t="inlineStr">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>07.02.01</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>Impozit si taxa pe cladiri (cod 07.02.01.01+07.02.01.02)</t>
+        </is>
+      </c>
+      <c r="D884" t="n">
+        <v>20025</v>
+      </c>
+      <c r="E884" t="n">
+        <v>20</v>
+      </c>
+      <c r="F884" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="G884" s="2" t="n">
+        <v>26500000</v>
+      </c>
+      <c r="H884" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" s="5" t="inlineStr">
+        <is>
+          <t>07.02.01.02</t>
+        </is>
+      </c>
+      <c r="B885" s="5" t="n"/>
+      <c r="C885" s="5" t="inlineStr">
         <is>
           <t>(rând derivat din formula tipărită)</t>
         </is>
       </c>
-      <c r="D884" s="5" t="n"/>
-      <c r="E884" s="5" t="n">
+      <c r="D885" s="5" t="n"/>
+      <c r="E885" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="F884" s="5" t="inlineStr">
+      <c r="F885" s="5" t="inlineStr">
         <is>
           <t>revenue</t>
         </is>
       </c>
-      <c r="G884" s="6" t="n">
-        <v>3750000</v>
-      </c>
-      <c r="H884" s="5" t="inlineStr">
+      <c r="G885" s="6" t="n">
+        <v>16500000</v>
+      </c>
+      <c r="H885" s="5" t="inlineStr">
         <is>
           <t>formula</t>
         </is>
       </c>
-      <c r="I884" s="5" t="inlineStr">
-        <is>
-          <t>rând absent, derivat aritmetic din formula părintelui 07.02; name mismatch vs nomenclator (37%): '(rând derivat din formula tipărită)' vs 'Alte impozite si taxe pe proprietate'</t>
-        </is>
-      </c>
-    </row>
-    <row r="885">
-      <c r="A885" s="3" t="inlineStr">
-        <is>
-          <t>07.02.01</t>
-        </is>
-      </c>
-      <c r="B885" s="3" t="n"/>
-      <c r="C885" s="3" t="inlineStr">
-        <is>
-          <t>Impozit si taxa pe cladiri (cod 07.02.01.01+07.02.01.02)</t>
-        </is>
-      </c>
-      <c r="D885" s="3" t="n">
-        <v>20025</v>
-      </c>
-      <c r="E885" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="F885" s="3" t="inlineStr">
-        <is>
-          <t>revenue</t>
-        </is>
-      </c>
-      <c r="G885" s="4" t="n">
-        <v>26500000</v>
-      </c>
-      <c r="H885" s="3" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I885" s="3" t="inlineStr">
-        <is>
-          <t>07.02.01 total_2026: parent 26.500.000,00 != sum(children) 16.500.000.015.500.000,00 (2 children)</t>
+      <c r="I885" s="5" t="inlineStr">
+        <is>
+          <t>rând absent, derivat aritmetic din formula părintelui 07.02.01; name mismatch vs nomenclator (43%): '(rând derivat din formula tipărită)' vs 'Impozit si taxa pe cladiri de la persoan'</t>
         </is>
       </c>
     </row>
@@ -29080,30 +29079,35 @@
       </c>
     </row>
     <row r="887">
-      <c r="A887" t="inlineStr">
+      <c r="A887" s="3" t="inlineStr">
         <is>
           <t>07.02.01.02</t>
         </is>
       </c>
-      <c r="C887" t="inlineStr">
+      <c r="B887" s="3" t="n"/>
+      <c r="C887" s="3" t="inlineStr">
         <is>
           <t>Impozit si taxa pe cladiri de la persoane juridice *)</t>
         </is>
       </c>
-      <c r="E887" t="n">
+      <c r="D887" s="3" t="n"/>
+      <c r="E887" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="F887" t="inlineStr">
+      <c r="F887" s="3" t="inlineStr">
         <is>
           <t>revenue</t>
         </is>
       </c>
-      <c r="G887" s="2" t="n">
-        <v>1.65000000055e+16</v>
-      </c>
-      <c r="H887" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="G887" s="4" t="n"/>
+      <c r="H887" s="3" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I887" s="3" t="inlineStr">
+        <is>
+          <t>unparseable cell '16.500.000,00 5.500.000,00' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -59488,7 +59492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F166"/>
+  <dimension ref="A1:F167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -60892,7 +60896,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>84.02</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -60902,14 +60906,14 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>84.02 total_2026: parent 72.143.520,00 != sum(children) 10.670.000,00 (2 children)</t>
+          <t>60 total_2026: parent 32.823.090,00 != sum(children) 27.750.000,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -60920,11 +60924,6 @@
       <c r="C53" t="n">
         <v>19</v>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>total_2026</t>
@@ -60932,7 +60931,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>60 total_2026: parent 32.823.090,00 != sum(children) 27.750.000,00 (1 children)</t>
+          <t>unparseable cell '5.073.090,00 7.439.730,00' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -60942,9 +60941,9 @@
           <t>V4_hierarchy</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>info</t>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -60952,24 +60951,29 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>07.02.50</t>
+          <t>07.02</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>rând absent, derivat aritmetic din formula părintelui 07.02</t>
+          <t>07.02 total_2026: parent 32.200.000,00 != sum(children) 26.500.000,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -60977,24 +60981,24 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>07.02.50</t>
+          <t>07.02.01.02</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (37%): '(rând derivat din formula tipărită)' vs 'Alte impozite si taxe pe proprietate'</t>
+          <t>rând absent, derivat aritmetic din formula părintelui 07.02.01</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -61002,24 +61006,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>07.02.01</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>07.02.01.02</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>07.02.01 total_2026: parent 26.500.000,00 != sum(children) 16.500.000.015.500.000,00 (2 children)</t>
+          <t>name mismatch vs nomenclator (43%): '(rând derivat din formula tipărită)' vs 'Impozit si taxa pe cladiri de la persoan'</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -61030,11 +61029,6 @@
       <c r="C57" t="n">
         <v>20</v>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>07.02.02</t>
-        </is>
-      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>total_2026</t>
@@ -61042,19 +61036,19 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>07.02.02 total_2026: parent 1.750.000,00 != sum(children) 3.750.000,00 (3 children)</t>
+          <t>unparseable cell '16.500.000,00 5.500.000,00' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -61062,37 +61056,42 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>07.02.02.01</t>
+          <t>07.02.02</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Impozit pe terenuri de la persoane fizic'</t>
+          <t>07.02.02 total_2026: parent 1.750.000,00 != sum(children) 3.750.000,00 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>07.02.02.01</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (0%): '' vs 'Impozit pe terenuri de la persoane fizic'</t>
         </is>
       </c>
     </row>
@@ -61199,12 +61198,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -61212,37 +61211,37 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>35.02.01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (26%): 'Vven   l td     t i .02' vs 'Venituri din amenzi si alte sanctiuni ap'</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>35.02.01</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (26%): 'Vven   l td     t i .02' vs 'Venituri din amenzi si alte sanctiuni ap'</t>
         </is>
       </c>
     </row>
@@ -61299,7 +61298,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V1_code</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -61312,42 +61311,42 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>49.02</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>49.02 total_2026: parent 188.260.750,00 != sum(children) 10.670.000,00 (2 children)</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>49.02</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (38%): 'Che od  t a e e d t iie  i ilor legale' vs 'Cheltuieli judiciare si extrajudiciare d'</t>
+          <t>49.02 total_2026: parent 188.260.750,00 != sum(children) 10.670.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -61363,16 +61362,16 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (24%): 'TITL  L  L L  L    INT' vs 'Titlul XXII Plăţi efectuate în anii prec'</t>
+          <t>name mismatch vs nomenclator (38%): 'Che od  t a e e d t iie  i ilor legale' vs 'Cheltuieli judiciare si extrajudiciare d'</t>
         </is>
       </c>
     </row>
@@ -61392,19 +61391,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>85.01.01</t>
+          <t>85</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (40%): 'Plautl  a et  es   e  i is urtd e e e lo' vs 'Plăţi efectuate în anii precedenţi şi re'</t>
+          <t>name mismatch vs nomenclator (24%): 'TITL  L  L L  L    INT' vs 'Titlul XXII Plăţi efectuate în anii prec'</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -61417,19 +61416,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>85.01.01</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>duplicate of p22 with different values</t>
+          <t>name mismatch vs nomenclator (40%): 'Plautl  a et  es   e  i is urtd e e e lo' vs 'Plăţi efectuate în anii precedenţi şi re'</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -61438,16 +61437,16 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (24%): 'TITL    I I      INT' vs 'Titlul XXII Plăţi efectuate în anii prec'</t>
+          <t>duplicate of p22 with different values</t>
         </is>
       </c>
     </row>
@@ -61467,62 +61466,62 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>85.01</t>
+          <t>85</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (18%): 'PLA         NT' vs 'Plăţi efectuate în anii precedenţi şi re'</t>
+          <t>name mismatch vs nomenclator (24%): 'TITL    I I      INT' vs 'Titlul XXII Plăţi efectuate în anii prec'</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>26</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+        <v>25</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>85.01</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>unparseable cell "00'0" in column total_2026</t>
+          <t>name mismatch vs nomenclator (18%): 'PLA         NT' vs 'Plăţi efectuate în anii precedenţi şi re'</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>28</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>85</t>
+        <v>26</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (29%): 'TITL    I I     E INT' vs 'Titlul XXII Plăţi efectuate în anii prec'</t>
+          <t>unparseable cell "00'0" in column total_2026</t>
         </is>
       </c>
     </row>
@@ -61542,49 +61541,49 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>85.01</t>
+          <t>85</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (26%): 'PLAD    I I    NT' vs 'Plăţi efectuate în anii precedenţi şi re'</t>
+          <t>name mismatch vs nomenclator (29%): 'TITL    I I     E INT' vs 'Titlul XXII Plăţi efectuate în anii prec'</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>67.02.50</t>
+          <t>85.01</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>rând absent, derivat aritmetic din formula părintelui 67.02</t>
+          <t>name mismatch vs nomenclator (26%): 'PLAD    I I    NT' vs 'Plăţi efectuate în anii precedenţi şi re'</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -61597,14 +61596,14 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (30%): '(rând derivat din formula tipărită)' vs 'Alte servicii în domeniile culturii, rec'</t>
+          <t>rând absent, derivat aritmetic din formula părintelui 67.02</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -61613,16 +61612,16 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>67.02.03</t>
+          <t>67.02.50</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>duplicate of p14 with different values</t>
+          <t>name mismatch vs nomenclator (30%): '(rând derivat din formula tipărită)' vs 'Alte servicii în domeniile culturii, rec'</t>
         </is>
       </c>
     </row>
@@ -61642,7 +61641,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>67.02.03.04</t>
+          <t>67.02.03</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -61667,7 +61666,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>67.02.03.06</t>
+          <t>67.02.03.04</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -61692,7 +61691,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>67.02.03.30</t>
+          <t>67.02.03.06</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -61717,7 +61716,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>67.02.05</t>
+          <t>67.02.03.30</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -61742,7 +61741,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>67.02.05.01</t>
+          <t>67.02.05</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -61767,7 +61766,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>67.02.05.03</t>
+          <t>67.02.05.01</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -61792,7 +61791,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>68.02</t>
+          <t>67.02.05.03</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -61813,16 +61812,16 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>68.02.04</t>
+          <t>68.02</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>duplicate of p16 with different values</t>
+          <t>duplicate of p14 with different values</t>
         </is>
       </c>
     </row>
@@ -61842,7 +61841,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>68.02.50</t>
+          <t>68.02.04</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -61867,7 +61866,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>68.02.50.50</t>
+          <t>68.02.50</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -61892,7 +61891,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>68.02.50.50</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -61904,7 +61903,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -61913,46 +61912,41 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (26%): 'TITL  L  I I      INT' vs 'Titlul XXII Plăţi efectuate în anii prec'</t>
+          <t>duplicate of p16 with different values</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B93" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>84.02</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>85</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>84.02 total_2026: parent 18.880.700,00 != sum(children) 72.143.520,00 (1 children)</t>
+          <t>name mismatch vs nomenclator (26%): 'TITL  L  I I      INT' vs 'Titlul XXII Plăţi efectuate în anii prec'</t>
         </is>
       </c>
     </row>
@@ -61982,32 +61976,37 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>84.02 total_2026: parent 18.880.700,00 != sum(children) 10.670.000,00 (2 children)</t>
+          <t>84.02 total_2026: parent 18.880.700,00 != sum(children) 72.143.520,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84.02</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (24%): 'TITL    I I      ENT' vs 'Titlul XXII Plăţi efectuate în anii prec'</t>
+          <t>84.02 total_2026: parent 18.880.700,00 != sum(children) 10.670.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -62027,19 +62026,19 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>85.01.01</t>
+          <t>85</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'Plaetl   e  s   e    rtd e e e ocal' vs 'Plăţi efectuate în anii precedenţi şi re'</t>
+          <t>name mismatch vs nomenclator (24%): 'TITL    I I      ENT' vs 'Titlul XXII Plăţi efectuate în anii prec'</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -62052,12 +62051,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>84.02.03</t>
+          <t>85.01.01</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>duplicate of p20 with different values</t>
+          <t>name mismatch vs nomenclator (28%): 'Plaetl   e  s   e    rtd e e e ocal' vs 'Plăţi efectuate în anii precedenţi şi re'</t>
         </is>
       </c>
     </row>
@@ -62077,7 +62076,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>84.02.03.01</t>
+          <t>84.02.03</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -62102,7 +62101,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>84.02.03.02</t>
+          <t>84.02.03.01</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -62127,7 +62126,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>99.02</t>
+          <t>84.02.03.02</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -62139,12 +62138,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B101" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -62152,12 +62151,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>99.02</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>duplicate of p20 with different values</t>
         </is>
       </c>
     </row>
@@ -62264,12 +62263,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -62282,19 +62281,19 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>duplicate of p2 with different values</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B107" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -62307,19 +62306,19 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>duplicate of p2 with different values</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -62332,7 +62331,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>duplicate of p2 with different values</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
@@ -62352,7 +62351,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -62364,12 +62363,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B110" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -62377,12 +62376,12 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>42.02</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>duplicate of p2 with different values</t>
         </is>
       </c>
     </row>
@@ -62414,12 +62413,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -62432,14 +62431,14 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>duplicate of p2 with different values</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -62448,23 +62447,23 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>42.02.88</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (14%): 'A10o0c.      e e     .0)' vs 'Alocări de sume din PNRR aferente asiste'</t>
+          <t>duplicate of p2 with different values</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -62477,12 +62476,12 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>43.02</t>
+          <t>42.02.88</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>name mismatch vs nomenclator (14%): 'A10o0c.      e e     .0)' vs 'Alocări de sume din PNRR aferente asiste'</t>
         </is>
       </c>
     </row>
@@ -62502,7 +62501,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>49.02</t>
+          <t>43.02</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -62527,7 +62526,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>49.02</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -62552,19 +62551,19 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>duplicate of p5 with different values</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -62573,16 +62572,16 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>56.49</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (25%): 'Pro -    (+       cod 56.49.01 la 56.49.' vs 'Programe finanțate din Fondul Social Eur'</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
@@ -62602,19 +62601,19 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>58.01</t>
+          <t>56.49</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (17%): 'Pro     (       .0()' vs 'Programe din Fondul European de Dezvolta'</t>
+          <t>name mismatch vs nomenclator (25%): 'Pro -    (+       cod 56.49.01 la 56.49.' vs 'Programe finanțate din Fondul Social Eur'</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -62627,24 +62626,24 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>50.02</t>
+          <t>58.01</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>duplicate of p6 with different values</t>
+          <t>name mismatch vs nomenclator (17%): 'Pro     (       .0()' vs 'Programe din Fondul European de Dezvolta'</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -62652,24 +62651,24 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>56.02</t>
+          <t>50.02</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>rând absent, derivat aritmetic din formula părintelui 50.02</t>
+          <t>duplicate of p6 with different values</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -62682,14 +62681,14 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (36%): '(rând derivat din formula tipărită)' vs 'Transferuri cu caracter general intre di'</t>
+          <t>rând absent, derivat aritmetic din formula părintelui 50.02</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -62702,12 +62701,12 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>51.02</t>
+          <t>56.02</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>duplicate of p6 with different values</t>
+          <t>name mismatch vs nomenclator (36%): '(rând derivat din formula tipărită)' vs 'Transferuri cu caracter general intre di'</t>
         </is>
       </c>
     </row>
@@ -62727,12 +62726,12 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>51.02.01</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>duplicate of p8 with different values</t>
+          <t>duplicate of p6 with different values</t>
         </is>
       </c>
     </row>
@@ -62752,7 +62751,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>51.02.01.03</t>
+          <t>51.02.01</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -62777,24 +62776,24 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>59.02</t>
+          <t>51.02.01.03</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>duplicate of p9 with different values</t>
+          <t>duplicate of p8 with different values</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -62802,24 +62801,24 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>60.02</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>rând absent, derivat aritmetic din formula părintelui 59.02</t>
+          <t>duplicate of p9 with different values</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -62832,14 +62831,14 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (24%): '(rând derivat din formula tipărită)' vs 'Aparare'</t>
+          <t>rând absent, derivat aritmetic din formula părintelui 59.02</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -62852,24 +62851,24 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>61.02</t>
+          <t>60.02</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>duplicate of p9 with different values</t>
+          <t>name mismatch vs nomenclator (24%): '(rând derivat din formula tipărită)' vs 'Aparare'</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -62877,24 +62876,24 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>61.02.50</t>
+          <t>61.02</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>rând absent, derivat aritmetic din formula părintelui 61.02</t>
+          <t>duplicate of p9 with different values</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -62907,14 +62906,14 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (35%): '(rând derivat din formula tipărită)' vs 'Alte cheltuieli în domeniul ordinii publ'</t>
+          <t>rând absent, derivat aritmetic din formula părintelui 61.02</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -62923,16 +62922,16 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>61.02.50</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>duplicate of p9 with different values</t>
+          <t>name mismatch vs nomenclator (35%): '(rând derivat din formula tipărită)' vs 'Alte cheltuieli în domeniul ordinii publ'</t>
         </is>
       </c>
     </row>
@@ -62952,7 +62951,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>61.02.03</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -62977,7 +62976,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>61.02.03.04</t>
+          <t>61.02.03</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -63002,7 +63001,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>61.02.05</t>
+          <t>61.02.03.04</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -63027,7 +63026,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>63.02</t>
+          <t>61.02.05</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -63052,7 +63051,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>65.02</t>
+          <t>63.02</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -63077,12 +63076,12 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>65.02.03</t>
+          <t>65.02</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>duplicate of p11 with different values</t>
+          <t>duplicate of p9 with different values</t>
         </is>
       </c>
     </row>
@@ -63102,7 +63101,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>65.02.03.01</t>
+          <t>65.02.03</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -63114,30 +63113,25 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B140" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>65.02.03.01</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>67.02 total_2026: parent 36.727.170,00 != sum(children) 5.039.170,00 (1 children)</t>
+          <t>duplicate of p11 with different values</t>
         </is>
       </c>
     </row>
@@ -63157,7 +63151,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>68.02</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -63167,19 +63161,19 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>68.02 total_2026: parent 6.775.750,00 != sum(children) 4.548.540,00 (1 children)</t>
+          <t>67.02 total_2026: parent 36.727.170,00 != sum(children) 5.039.170,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -63187,42 +63181,42 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>58.01</t>
+          <t>68.02</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (34%): 'CADRULUI FINANCIAR 2014- 2020 Pro  l    ' vs 'Programe din Fondul European de Dezvolta'</t>
+          <t>68.02 total_2026: parent 6.775.750,00 != sum(children) 4.548.540,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B143" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>70.02</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>58.01</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>70.02 total_2026: parent 72.817.070,00 != sum(children) 82.622.710,00 (4 children)</t>
+          <t>name mismatch vs nomenclator (34%): 'CADRULUI FINANCIAR 2014- 2020 Pro  l    ' vs 'Programe din Fondul European de Dezvolta'</t>
         </is>
       </c>
     </row>
@@ -63252,19 +63246,19 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>70.02 total_2026: parent 72.817.070,00 != sum(children) 19.058.980,00 (2 children)</t>
+          <t>70.02 total_2026: parent 72.817.070,00 != sum(children) 82.622.710,00 (4 children)</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -63272,19 +63266,24 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>70.02</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (17%): 'Tile  e e  e e      R' vs 'Titlul XIII „Proiecte cu finanțare din s'</t>
+          <t>70.02 total_2026: parent 72.817.070,00 != sum(children) 19.058.980,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -63297,24 +63296,24 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>70.02.03</t>
+          <t>61</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>duplicate of p17 with different values</t>
+          <t>name mismatch vs nomenclator (17%): 'Tile  e e  e e      R' vs 'Titlul XIII „Proiecte cu finanțare din s'</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -63322,24 +63321,24 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>70.02.03.01</t>
+          <t>70.02.03</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>rând absent, derivat aritmetic din formula părintelui 70.02.03</t>
+          <t>duplicate of p17 with different values</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -63352,14 +63351,14 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (41%): '(rând derivat din formula tipărită)' vs 'Dezvoltarea sistemului de locuinte'</t>
+          <t>rând absent, derivat aritmetic din formula părintelui 70.02.03</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -63372,12 +63371,12 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>70.02.03.30</t>
+          <t>70.02.03.01</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>duplicate of p17 with different values</t>
+          <t>name mismatch vs nomenclator (41%): '(rând derivat din formula tipărită)' vs 'Dezvoltarea sistemului de locuinte'</t>
         </is>
       </c>
     </row>
@@ -63397,7 +63396,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>70.02.05</t>
+          <t>70.02.03.30</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -63409,12 +63408,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -63422,24 +63421,24 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>70.02.05.02</t>
+          <t>70.02.05</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>rând absent, derivat aritmetic din formula părintelui 70.02.05</t>
+          <t>duplicate of p17 with different values</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -63452,14 +63451,14 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): '(rând derivat din formula tipărită)' vs 'Amenajari hidrotehnice'</t>
+          <t>rând absent, derivat aritmetic din formula părintelui 70.02.05</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -63472,12 +63471,12 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>70.02.05.01</t>
+          <t>70.02.05.02</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>duplicate of p17 with different values</t>
+          <t>name mismatch vs nomenclator (32%): '(rând derivat din formula tipărită)' vs 'Amenajari hidrotehnice'</t>
         </is>
       </c>
     </row>
@@ -63497,7 +63496,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>70.02.06</t>
+          <t>70.02.05.01</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -63522,7 +63521,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>70.02.50</t>
+          <t>70.02.06</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -63547,7 +63546,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>74.02</t>
+          <t>70.02.50</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -63568,16 +63567,16 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>74.02.03</t>
+          <t>74.02</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>duplicate of p18 with different values</t>
+          <t>duplicate of p17 with different values</t>
         </is>
       </c>
     </row>
@@ -63597,7 +63596,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>74.02.05</t>
+          <t>74.02.03</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -63622,7 +63621,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>74.02.05.01</t>
+          <t>74.02.05</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -63647,7 +63646,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>79.02</t>
+          <t>74.02.05.01</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -63672,7 +63671,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.02</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -63684,12 +63683,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -63697,24 +63696,24 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>80.02.02</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>rând absent, derivat aritmetic din formula părintelui 80.02</t>
+          <t>duplicate of p18 with different values</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -63727,14 +63726,14 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (37%): '(rând derivat din formula tipărită)' vs 'Actiuni generale de munca'</t>
+          <t>rând absent, derivat aritmetic din formula părintelui 80.02</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -63747,12 +63746,12 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>80.02.01</t>
+          <t>80.02.02</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>duplicate of p18 with different values</t>
+          <t>name mismatch vs nomenclator (37%): '(rând derivat din formula tipărită)' vs 'Actiuni generale de munca'</t>
         </is>
       </c>
     </row>
@@ -63772,7 +63771,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>80.02.01.30</t>
+          <t>80.02.01</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -63784,12 +63783,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B166" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -63797,15 +63796,40 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
+          <t>80.02.01.30</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>duplicate of p18 with different values</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>41</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
           <t>84.02</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr">
+      <c r="E167" t="inlineStr">
         <is>
           <t>total_2026</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr">
+      <c r="F167" t="inlineStr">
         <is>
           <t>84.02 total_2026: parent 53.262.820,00 != sum(children) 7.439.730,00 (1 children)</t>
         </is>
@@ -63822,7 +63846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -63844,7 +63868,7 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Documente</t>
+          <t>Schema calitate</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -63854,60 +63878,230 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>Linii de date</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1752</v>
+          <t>Metrica de calitate</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>observed_strict_line_rate</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Linii fara probleme</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1607</v>
+          <t>Recall masurat</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>nu</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>% curat</t>
+          <t>Documente</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>91.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Erori</t>
+          <t>Linii de date</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>61</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Avertismente</t>
+          <t>Linii strict verificate</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>95</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
+          <t>% linii strict verificate</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>91.7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Celule numerice</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1606</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>% celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>91.90000000000001</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Pagini asteptate</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Pagini selectate</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Pagini procesate</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>PDF complet</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Linii fara probleme</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1607</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>% curat</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>91.7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Erori</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Avertismente</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Informatii</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Schema publicare</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Bundle conversie</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ef6b1f4774d85f31d354b3e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>SHA-256 PDF sursa</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>71ca1b3eeff73fc5dd5092a000783a7db1f2b5a33690f4eefe68a536c4f704b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
           <t>— Anexa (de la pagina 1)</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>local, pag. 1-41, 1821 linii</t>
         </is>
